--- a/data/trans_orig/RUIDO_1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26764</t>
+          <t>25216</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23539</t>
+          <t>24175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35836</t>
+          <t>37004</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39015</t>
+          <t>43853</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>167</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43636</t>
+          <t>45898</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40868</t>
+          <t>37416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44843</t>
+          <t>44731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36637</t>
+          <t>37399</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73641</t>
+          <t>75573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108974</t>
+          <t>107297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153310</t>
+          <t>153629</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97252</t>
+          <t>97112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127686</t>
+          <t>126996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218530</t>
+          <t>216859</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>273071</t>
+          <t>271584</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,77 +2336,77 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7562</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1888</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>8163</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>10192</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1888</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>8564</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11091</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>19548</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>169</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19533</t>
+          <t>19908</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33777</t>
+          <t>34647</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42699</t>
+          <t>41965</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13157</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32902</t>
+          <t>33241</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>14661</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31195</t>
+          <t>32213</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32085</t>
+          <t>30795</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57016</t>
+          <t>57201</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>115312</t>
+          <t>115198</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>147192</t>
+          <t>147324</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138767</t>
+          <t>140388</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>163637</t>
+          <t>163369</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>264286</t>
+          <t>261166</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>304014</t>
+          <t>303365</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,83%</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13789</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3465,77 +3465,77 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1543</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>7066</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2954</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>14761</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1543</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5605</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>7066</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>2782</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>14760</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>873</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>765</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>829</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>18449</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>582</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>20421</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25499</t>
+          <t>27386</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>26073</t>
+          <t>25920</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>24384</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>46799</t>
+          <t>46674</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>25444</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>47285</t>
+          <t>46294</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18975</t>
+          <t>19897</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>33904</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>49526</t>
+          <t>50284</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>76704</t>
+          <t>77304</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>199523</t>
+          <t>198988</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>231782</t>
+          <t>230296</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>179854</t>
+          <t>179228</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>202443</t>
+          <t>201753</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>384675</t>
+          <t>385004</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>424707</t>
+          <t>424859</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>519</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>753</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5262,12 +5262,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>15193</t>
+          <t>14387</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>138694</t>
+          <t>139414</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>170069</t>
+          <t>150175</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>17841</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>23118</t>
+          <t>23805</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>20196</t>
+          <t>21237</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>23399</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>18784</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>37826</t>
+          <t>38110</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>34023</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>58899</t>
+          <t>57682</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>22265</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>41466</t>
+          <t>41319</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>61415</t>
+          <t>61942</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>93629</t>
+          <t>92771</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>229757</t>
+          <t>230380</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>262372</t>
+          <t>262863</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>177172</t>
+          <t>179706</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>285756</t>
+          <t>284753</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>417293</t>
+          <t>416134</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>535601</t>
+          <t>535822</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -6396,12 +6396,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -6622,12 +6622,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>15511</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>11261</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>22889</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>25137</t>
+          <t>25502</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>22917</t>
+          <t>24403</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>42900</t>
+          <t>45012</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>24085</t>
+          <t>23188</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>43570</t>
+          <t>42673</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>24789</t>
+          <t>24790</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>39519</t>
+          <t>39505</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>53128</t>
+          <t>52372</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>76452</t>
+          <t>76700</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>231771</t>
+          <t>231962</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>259456</t>
+          <t>258872</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>213713</t>
+          <t>213545</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>234825</t>
+          <t>234912</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>452596</t>
+          <t>452485</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>485171</t>
+          <t>486606</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -7643,12 +7643,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>976</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>240</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7869,12 +7869,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>500</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -8208,12 +8208,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>911</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>12598</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -8434,12 +8434,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>23679</t>
+          <t>23006</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8547,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>12745</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>24898</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>40506</t>
+          <t>39334</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>59076</t>
+          <t>59254</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>144186</t>
+          <t>145101</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>162766</t>
+          <t>163117</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>333930</t>
+          <t>334575</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>395187</t>
+          <t>396035</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>483961</t>
+          <t>484042</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>575828</t>
+          <t>572599</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -8890,12 +8890,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9131,12 +9131,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9229,12 +9229,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9244,12 +9244,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>380</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -9681,12 +9681,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>896</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>330</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>17322</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>21049</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9922,12 +9922,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>15679</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>27944</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>28839</t>
+          <t>28170</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>43933</t>
+          <t>44388</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>113959</t>
+          <t>114082</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>128659</t>
+          <t>129292</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10035,12 +10035,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>197497</t>
+          <t>197448</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>211667</t>
+          <t>211807</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>316361</t>
+          <t>316559</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>336855</t>
+          <t>337366</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,3%</t>
         </is>
       </c>
     </row>
@@ -10250,12 +10250,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10265,12 +10265,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>26502</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10363,12 +10363,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10378,12 +10378,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10398,12 +10398,12 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>33378</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -10476,12 +10476,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10511,12 +10511,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -10589,12 +10589,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>6895</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>25575</t>
+          <t>24974</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>41402</t>
+          <t>41985</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>40562</t>
+          <t>39914</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>17883</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>19008</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>49739</t>
+          <t>51708</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -10928,12 +10928,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>19410</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>49238</t>
+          <t>50759</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>36493</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>219719</t>
+          <t>188811</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10998,12 +10998,12 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>65841</t>
+          <t>65088</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>222454</t>
+          <t>259745</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -11041,12 +11041,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>21897</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>50961</t>
+          <t>46900</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>24890</t>
+          <t>24483</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>37181</t>
+          <t>37468</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>67932</t>
+          <t>67960</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>70481</t>
+          <t>71986</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>123487</t>
+          <t>121176</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>50614</t>
+          <t>52719</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>90751</t>
+          <t>90402</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>130996</t>
+          <t>130783</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>198483</t>
+          <t>200021</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -11267,12 +11267,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>163434</t>
+          <t>164745</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>214241</t>
+          <t>218285</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>126074</t>
+          <t>129541</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>213934</t>
+          <t>213533</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>301026</t>
+          <t>303378</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>413309</t>
+          <t>412655</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -11380,12 +11380,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>1208325</t>
+          <t>1204150</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>1287758</t>
+          <t>1291266</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>1434953</t>
+          <t>1435429</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1631081</t>
+          <t>1623612</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -11430,12 +11430,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11450,12 +11450,12 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>2679933</t>
+          <t>2672528</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>2910240</t>
+          <t>2904034</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Edad-trans_orig.xlsx
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>22905</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25216</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>27323</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24175</t>
+          <t>25547</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>20547</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>42684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18441</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43853</t>
+          <t>30342</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>19860</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45898</t>
+          <t>37579</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>20615</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37416</t>
+          <t>35032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30699</t>
+          <t>30978</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19168</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44731</t>
+          <t>48391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>53250</t>
+          <t>51593</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37399</t>
+          <t>36148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75573</t>
+          <t>71643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>133042</t>
+          <t>135942</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107297</t>
+          <t>115198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153629</t>
+          <t>152653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>113406</t>
+          <t>132918</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97112</t>
+          <t>115931</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126996</t>
+          <t>147080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>246447</t>
+          <t>268861</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216859</t>
+          <t>241818</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>271584</t>
+          <t>293860</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>187370</t>
+          <t>184018</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>187370</t>
+          <t>184018</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>187370</t>
+          <t>184018</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>157297</t>
+          <t>181193</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>157297</t>
+          <t>181193</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>157297</t>
+          <t>181193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>344666</t>
+          <t>365212</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>344666</t>
+          <t>365212</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>344666</t>
+          <t>365212</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>15934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2773,12 +2773,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>14605</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>16866</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -2876,32 +2876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19908</t>
+          <t>22100</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20778</t>
+          <t>24773</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34647</t>
+          <t>42409</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>27714</t>
+          <t>34422</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>22211</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41965</t>
+          <t>51647</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>24558</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33241</t>
+          <t>35500</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>21587</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32213</t>
+          <t>33430</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>43652</t>
+          <t>47402</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30795</t>
+          <t>35762</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57201</t>
+          <t>62147</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -3215,32 +3215,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>131708</t>
+          <t>149880</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>115198</t>
+          <t>131834</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>147324</t>
+          <t>166841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3250,32 +3250,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>152658</t>
+          <t>173191</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140388</t>
+          <t>159491</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>163369</t>
+          <t>185299</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>284366</t>
+          <t>323071</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>261166</t>
+          <t>299077</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>303365</t>
+          <t>343177</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -3328,17 +3328,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>186824</t>
+          <t>216159</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>186824</t>
+          <t>216159</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>186824</t>
+          <t>216159</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>197996</t>
+          <t>223814</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>197996</t>
+          <t>223814</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>197996</t>
+          <t>223814</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>384820</t>
+          <t>439973</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>384820</t>
+          <t>439973</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>384820</t>
+          <t>439973</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3445,32 +3445,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>14865</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>8347</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14761</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3558,32 +3558,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3593,32 +3593,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>751</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>809</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>809</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,32 +3932,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,32 +3967,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4010,32 +4010,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>847</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4123,32 +4123,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4158,32 +4158,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -4236,32 +4236,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>19088</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,32 +4271,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>550</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>11215</t>
+          <t>11375</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>21020</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>15996</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>33684</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>20119</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11945</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>25920</t>
+          <t>29128</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>34219</t>
+          <t>40809</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>29955</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>46674</t>
+          <t>55016</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -4462,32 +4462,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>34771</t>
+          <t>38752</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>25444</t>
+          <t>27824</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>46294</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4497,32 +4497,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>26267</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19897</t>
+          <t>22613</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>34720</t>
+          <t>40124</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>61038</t>
+          <t>69714</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>50284</t>
+          <t>55853</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>77304</t>
+          <t>84326</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -4575,32 +4575,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>215894</t>
+          <t>248529</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>198988</t>
+          <t>231963</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>230296</t>
+          <t>266965</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4610,32 +4610,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>191155</t>
+          <t>218770</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>179228</t>
+          <t>204634</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>201753</t>
+          <t>230658</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>407049</t>
+          <t>467299</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>385004</t>
+          <t>444962</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>424859</t>
+          <t>488492</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -4688,17 +4688,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>295367</t>
+          <t>337875</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>295367</t>
+          <t>337875</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>295367</t>
+          <t>337875</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4723,17 +4723,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>257379</t>
+          <t>293917</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>257379</t>
+          <t>293917</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>257379</t>
+          <t>293917</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>552746</t>
+          <t>631791</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>552746</t>
+          <t>631791</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>552746</t>
+          <t>631791</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4840,32 +4840,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,32 +4875,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4953,32 +4953,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,32 +4988,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>692</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -5257,22 +5257,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5292,32 +5292,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>16228</t>
+          <t>17650</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -5370,32 +5370,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,32 +5440,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>40926</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>139414</t>
+          <t>15327</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>47774</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>150175</t>
+          <t>24957</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -5596,32 +5596,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>17841</t>
+          <t>17058</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5631,22 +5631,22 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>23805</t>
+          <t>23083</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>11349</t>
+          <t>12485</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>22667</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5744,32 +5744,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>15819</t>
+          <t>17250</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>23399</t>
+          <t>24914</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>27169</t>
+          <t>29735</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>18784</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>38110</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -5822,32 +5822,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>44766</t>
+          <t>48658</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>36147</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>57682</t>
+          <t>60406</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5857,32 +5857,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>32313</t>
+          <t>35498</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>22265</t>
+          <t>27538</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>41319</t>
+          <t>45095</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>77079</t>
+          <t>84156</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>61942</t>
+          <t>70267</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>92771</t>
+          <t>100219</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5935,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>246856</t>
+          <t>259805</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>230380</t>
+          <t>243392</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>262863</t>
+          <t>276096</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5970,32 +5970,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>255331</t>
+          <t>276922</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>179706</t>
+          <t>264466</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>284753</t>
+          <t>289625</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>502188</t>
+          <t>536727</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>416134</t>
+          <t>515358</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>535822</t>
+          <t>557364</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -6048,17 +6048,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>333830</t>
+          <t>351294</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>333830</t>
+          <t>351294</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>333830</t>
+          <t>351294</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6083,17 +6083,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>359337</t>
+          <t>354008</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>359337</t>
+          <t>354008</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>359337</t>
+          <t>354008</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>693168</t>
+          <t>705302</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>693168</t>
+          <t>705302</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>693168</t>
+          <t>705302</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>952</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -6278,32 +6278,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6348,32 +6348,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>707</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>707</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -6617,32 +6617,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6652,32 +6652,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>9423</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6687,32 +6687,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>15407</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6765,32 +6765,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6878,17 +6878,17 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>11261</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -6956,32 +6956,32 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6991,32 +6991,32 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -7069,32 +7069,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>13665</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>23338</t>
+          <t>24938</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7104,32 +7104,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>25502</t>
+          <t>28339</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7139,32 +7139,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>32172</t>
+          <t>35519</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>24403</t>
+          <t>25572</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>45012</t>
+          <t>49000</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -7182,32 +7182,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>32091</t>
+          <t>34376</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>23188</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>42673</t>
+          <t>45982</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7217,32 +7217,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>34494</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>24790</t>
+          <t>26967</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>39505</t>
+          <t>43956</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>63822</t>
+          <t>68870</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>52372</t>
+          <t>57588</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>82961</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -7295,32 +7295,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>245795</t>
+          <t>267866</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>231962</t>
+          <t>252061</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>258872</t>
+          <t>281403</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7330,32 +7330,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>224672</t>
+          <t>249364</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>213545</t>
+          <t>236321</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>234912</t>
+          <t>260289</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,32 +7365,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>470466</t>
+          <t>517230</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>452485</t>
+          <t>497915</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>486606</t>
+          <t>535755</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,25%</t>
         </is>
       </c>
     </row>
@@ -7408,17 +7408,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>307098</t>
+          <t>333182</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>307098</t>
+          <t>333182</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>307098</t>
+          <t>333182</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>294170</t>
+          <t>326243</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>294170</t>
+          <t>326243</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>294170</t>
+          <t>326243</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7478,17 +7478,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>601267</t>
+          <t>659425</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>601267</t>
+          <t>659425</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>601267</t>
+          <t>659425</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -7638,32 +7638,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>666</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7708,32 +7708,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>925</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -7987,12 +7987,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>350</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8160,32 +8160,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>927</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -8203,32 +8203,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>9884</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8273,32 +8273,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -8316,32 +8316,32 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8351,32 +8351,32 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8386,32 +8386,32 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6854</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -8429,32 +8429,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>14428</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8464,32 +8464,32 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>15048</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>21972</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -8542,32 +8542,32 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>26944</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8577,32 +8577,32 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>19640</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>39334</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8612,32 +8612,32 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>36190</t>
+          <t>39023</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>30871</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>59254</t>
+          <t>47905</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -8655,32 +8655,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>154712</t>
+          <t>171105</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>145101</t>
+          <t>161149</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>163117</t>
+          <t>181064</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8690,32 +8690,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>372236</t>
+          <t>184106</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>334575</t>
+          <t>176373</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>396035</t>
+          <t>191149</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>526948</t>
+          <t>355211</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>484042</t>
+          <t>342656</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>572599</t>
+          <t>366656</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -8768,17 +8768,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>194524</t>
+          <t>214727</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>194524</t>
+          <t>214727</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>194524</t>
+          <t>214727</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8803,17 +8803,17 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>405213</t>
+          <t>221088</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>405213</t>
+          <t>221088</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>405213</t>
+          <t>221088</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8838,17 +8838,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>599737</t>
+          <t>435815</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>599737</t>
+          <t>435815</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>599737</t>
+          <t>435815</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>615</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>658</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -9043,12 +9043,12 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9068,32 +9068,32 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>803</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -9382,12 +9382,12 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9407,22 +9407,22 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>401</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9520,32 +9520,32 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -9563,32 +9563,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>897</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9633,32 +9633,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>10971</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -9676,32 +9676,32 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>466</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9746,32 +9746,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -9789,32 +9789,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9824,32 +9824,32 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9859,32 +9859,32 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>11650</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -9902,32 +9902,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>14527</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>21049</t>
+          <t>21718</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9937,32 +9937,32 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>22656</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>15679</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>27392</t>
+          <t>30537</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9972,32 +9972,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>35467</t>
+          <t>38052</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>28170</t>
+          <t>30260</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>44388</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -10015,32 +10015,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>122062</t>
+          <t>132244</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>114082</t>
+          <t>123928</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>129292</t>
+          <t>139616</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10050,32 +10050,32 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>205124</t>
+          <t>221991</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>197448</t>
+          <t>213167</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>211807</t>
+          <t>229082</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10085,32 +10085,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>327187</t>
+          <t>354235</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>316559</t>
+          <t>342049</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>337366</t>
+          <t>365371</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -10128,17 +10128,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>150023</t>
+          <t>163820</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>150023</t>
+          <t>163820</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>150023</t>
+          <t>163820</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10163,17 +10163,17 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>236404</t>
+          <t>256218</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>236404</t>
+          <t>256218</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>236404</t>
+          <t>256218</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10198,17 +10198,17 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>386427</t>
+          <t>420038</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>386427</t>
+          <t>420038</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>386427</t>
+          <t>420038</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -10245,32 +10245,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>20999</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10280,32 +10280,32 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10315,32 +10315,32 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>16426</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>26465</t>
+          <t>30374</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -10358,32 +10358,32 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>26548</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10393,32 +10393,32 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>16392</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10428,32 +10428,32 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>33378</t>
+          <t>37994</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -10471,32 +10471,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10506,32 +10506,32 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>10337</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10541,32 +10541,32 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -10619,32 +10619,32 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10654,17 +10654,17 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>718</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -10697,67 +10697,67 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15378</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>25418</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>16609</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>10283</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>25735</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>14436</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>8655</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>22806</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>29132</t>
+          <t>31987</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>22236</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>41985</t>
+          <t>44226</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>39914</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>30308</t>
+          <t>29642</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>19808</t>
+          <t>20047</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>51708</t>
+          <t>45832</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -10923,32 +10923,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>18591</t>
+          <t>22755</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>50759</t>
+          <t>54062</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -10958,22 +10958,22 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>74209</t>
+          <t>45511</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>34259</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>188811</t>
+          <t>62424</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10993,32 +10993,32 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>105131</t>
+          <t>79792</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>65088</t>
+          <t>61259</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>259745</t>
+          <t>105655</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -11036,32 +11036,32 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>23169</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>46900</t>
+          <t>51769</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -11071,32 +11071,32 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>24483</t>
+          <t>26971</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11106,32 +11106,32 @@
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>50184</t>
+          <t>53286</t>
         </is>
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>40691</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>67960</t>
+          <t>71851</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -11149,32 +11149,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>92646</t>
+          <t>99664</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>71986</t>
+          <t>76745</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>121176</t>
+          <t>125156</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11184,32 +11184,32 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>73667</t>
+          <t>87540</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>52719</t>
+          <t>73669</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>90402</t>
+          <t>104752</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11219,32 +11219,32 @@
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>166314</t>
+          <t>187204</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>130783</t>
+          <t>161253</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>200021</t>
+          <t>217540</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -11262,32 +11262,32 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>188942</t>
+          <t>201737</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>164745</t>
+          <t>175067</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>218285</t>
+          <t>228300</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11297,32 +11297,32 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>181557</t>
+          <t>197074</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>129541</t>
+          <t>175469</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>213533</t>
+          <t>223696</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11332,32 +11332,32 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>370499</t>
+          <t>398811</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>303378</t>
+          <t>364533</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>412655</t>
+          <t>435574</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -11375,32 +11375,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1250069</t>
+          <t>1365372</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>1204150</t>
+          <t>1320587</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>1291266</t>
+          <t>1407764</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11410,32 +11410,32 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>1514580</t>
+          <t>1457263</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>1435429</t>
+          <t>1424488</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1623612</t>
+          <t>1486307</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11445,32 +11445,32 @@
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>2764650</t>
+          <t>2822634</t>
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>2672528</t>
+          <t>2772875</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>2904034</t>
+          <t>2873058</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -11488,17 +11488,17 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -11523,17 +11523,17 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -11558,17 +11558,17 @@
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">

--- a/data/trans_orig/RUIDO_1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
